--- a/tests/importers/fixtures/synthetic_btg_statement.xlsx
+++ b/tests/importers/fixtures/synthetic_btg_statement.xlsx
@@ -453,7 +453,7 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Renda Fixa</t>
         </is>
@@ -461,7 +461,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Posições</t>
         </is>
@@ -469,7 +469,7 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Posição &gt; LCI</t>
         </is>
@@ -515,7 +515,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Posições Detalhadas</t>
         </is>
@@ -523,7 +523,7 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Detalhamento &gt; LCI | ASSOCIACAO DE POUPANCA E EMPRESTIMO POUPEX</t>
         </is>
@@ -680,7 +680,7 @@
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Detalhamento &gt; LCA | BANCO DO BRASIL</t>
         </is>
@@ -834,7 +834,7 @@
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Posição Consolidada Por Emissor</t>
         </is>

--- a/tests/importers/fixtures/synthetic_btg_statement.xlsx
+++ b/tests/importers/fixtures/synthetic_btg_statement.xlsx
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45366</v>
+        <v>45301</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>46096</v>
